--- a/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7524" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7525" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:58:51+00:00</t>
+    <t>2024-11-06T10:59:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1280,8 +1280,23 @@
     <t>Bundle.entry:Hauptversicherter.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient {http://example.org/StructureDefinition/Hauptversicherter}
+    <t xml:space="preserve">Person {http://example.org/StructureDefinition/Hauptversicherter}
 </t>
+  </si>
+  <si>
+    <t>A generic person record</t>
+  </si>
+  <si>
+    <t>Demographics and administrative information about a person independent of a specific health-related context.</t>
+  </si>
+  <si>
+    <t>The Person resource does justice to person registries that keep track of persons regardless of their role. The Person resource is also a primary resource to point to for people acting in a particular role such as SubjectofCare, Practitioner, and Agent. Very few attributes are specific to any role and so Person is kept lean. Most attributes are expected to be tied to the role the Person plays rather than the Person himself. Examples of that are Guardian (SubjectofCare), ContactParty (SubjectOfCare, Practitioner), and multipleBirthInd (SubjectofCare).</t>
+  </si>
+  <si>
+    <t>administrative.entity</t>
+  </si>
+  <si>
+    <t>Entity, Role, or Act,Person(classCode="PSN" and determinerCode="INST" and quantity="1")</t>
   </si>
   <si>
     <t>Bundle.entry:Hauptversicherter.search</t>
@@ -1855,7 +1870,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.1328125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="68.70703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="86.15234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="42.9765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -18866,7 +18881,7 @@
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -18888,12 +18903,14 @@
         <v>402</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -18957,21 +18974,21 @@
         <v>20</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>367</v>
+        <v>407</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>204</v>
@@ -19083,7 +19100,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>208</v>
@@ -19195,7 +19212,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>209</v>
@@ -19309,7 +19326,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>210</v>
@@ -19425,7 +19442,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>211</v>
@@ -19539,7 +19556,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>217</v>
@@ -19653,7 +19670,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>222</v>
@@ -19765,7 +19782,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>226</v>
@@ -19877,7 +19894,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>227</v>
@@ -19991,7 +20008,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>228</v>
@@ -20107,7 +20124,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>229</v>
@@ -20219,7 +20236,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>235</v>
@@ -20333,7 +20350,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>239</v>
@@ -20445,7 +20462,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>242</v>
@@ -20557,7 +20574,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>245</v>
@@ -20669,7 +20686,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>248</v>
@@ -20781,7 +20798,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>251</v>
@@ -20893,7 +20910,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>255</v>
@@ -21005,7 +21022,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>256</v>
@@ -21119,7 +21136,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>257</v>
@@ -21235,7 +21252,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>258</v>
@@ -21347,7 +21364,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>261</v>
@@ -21459,7 +21476,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>264</v>
@@ -21573,7 +21590,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>268</v>
@@ -21687,7 +21704,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>272</v>
@@ -21801,13 +21818,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>181</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>20</v>
@@ -21915,7 +21932,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>188</v>
@@ -22027,7 +22044,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>189</v>
@@ -22141,7 +22158,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>190</v>
@@ -22257,7 +22274,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>191</v>
@@ -22369,7 +22386,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>194</v>
@@ -22483,7 +22500,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>199</v>
@@ -22509,13 +22526,13 @@
         <v>20</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22581,13 +22598,13 @@
         <v>20</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>20</v>
@@ -22595,7 +22612,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>204</v>
@@ -22707,7 +22724,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>208</v>
@@ -22819,7 +22836,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>209</v>
@@ -22933,7 +22950,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>210</v>
@@ -23049,7 +23066,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>211</v>
@@ -23163,7 +23180,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>217</v>
@@ -23277,7 +23294,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>222</v>
@@ -23389,7 +23406,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>226</v>
@@ -23501,7 +23518,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>227</v>
@@ -23615,7 +23632,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>228</v>
@@ -23731,7 +23748,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>229</v>
@@ -23843,7 +23860,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>235</v>
@@ -23957,7 +23974,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>239</v>
@@ -24069,7 +24086,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>242</v>
@@ -24181,7 +24198,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>245</v>
@@ -24293,7 +24310,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>248</v>
@@ -24405,7 +24422,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>251</v>
@@ -24517,7 +24534,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>255</v>
@@ -24629,7 +24646,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>256</v>
@@ -24743,7 +24760,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>257</v>
@@ -24859,7 +24876,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>258</v>
@@ -24971,7 +24988,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>261</v>
@@ -25083,7 +25100,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>264</v>
@@ -25197,7 +25214,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>268</v>
@@ -25311,7 +25328,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>272</v>
@@ -25425,10 +25442,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25451,19 +25468,19 @@
         <v>89</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25512,7 +25529,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -25541,10 +25558,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25567,16 +25584,16 @@
         <v>89</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -25626,7 +25643,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -25635,7 +25652,7 @@
         <v>88</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AJ210" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
+++ b/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-MOPEDAufnahmeBundle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7525" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7524" uniqueCount="482">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:59:22+00:00</t>
+    <t>2024-11-06T11:18:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1280,23 +1280,17 @@
     <t>Bundle.entry:Hauptversicherter.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Person {http://example.org/StructureDefinition/Hauptversicherter}
+    <t xml:space="preserve">RelatedPerson {http://example.org/StructureDefinition/Hauptversicherter}
 </t>
   </si>
   <si>
-    <t>A generic person record</t>
-  </si>
-  <si>
-    <t>Demographics and administrative information about a person independent of a specific health-related context.</t>
-  </si>
-  <si>
-    <t>The Person resource does justice to person registries that keep track of persons regardless of their role. The Person resource is also a primary resource to point to for people acting in a particular role such as SubjectofCare, Practitioner, and Agent. Very few attributes are specific to any role and so Person is kept lean. Most attributes are expected to be tied to the role the Person plays rather than the Person himself. Examples of that are Guardian (SubjectofCare), ContactParty (SubjectOfCare, Practitioner), and multipleBirthInd (SubjectofCare).</t>
-  </si>
-  <si>
-    <t>administrative.entity</t>
-  </si>
-  <si>
-    <t>Entity, Role, or Act,Person(classCode="PSN" and determinerCode="INST" and quantity="1")</t>
+    <t>A person that is related to a patient, but who is not a direct target of care</t>
+  </si>
+  <si>
+    <t>Information about a person that is involved in a patient's health or the care for a patient, but who is not the target of healthcare, nor has a formal responsibility in the care process.</t>
+  </si>
+  <si>
+    <t>Entity, Role, or Act,role</t>
   </si>
   <si>
     <t>Bundle.entry:Hauptversicherter.search</t>
@@ -1870,7 +1864,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.1328125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="86.15234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="68.70703125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="42.9765625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -18908,9 +18902,7 @@
       <c r="M151" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="N151" t="s" s="2">
-        <v>405</v>
-      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>20</v>
@@ -18974,13 +18966,13 @@
         <v>20</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>20</v>
@@ -18988,7 +18980,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>204</v>
@@ -19100,7 +19092,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>208</v>
@@ -19212,7 +19204,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>209</v>
@@ -19326,7 +19318,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>210</v>
@@ -19442,7 +19434,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>211</v>
@@ -19556,7 +19548,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>217</v>
@@ -19670,7 +19662,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>222</v>
@@ -19782,7 +19774,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>226</v>
@@ -19894,7 +19886,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>227</v>
@@ -20008,7 +20000,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>228</v>
@@ -20124,7 +20116,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>229</v>
@@ -20236,7 +20228,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>235</v>
@@ -20350,7 +20342,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>239</v>
@@ -20462,7 +20454,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>242</v>
@@ -20574,7 +20566,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>245</v>
@@ -20686,7 +20678,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>248</v>
@@ -20798,7 +20790,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>251</v>
@@ -20910,7 +20902,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>255</v>
@@ -21022,7 +21014,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>256</v>
@@ -21136,7 +21128,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>257</v>
@@ -21252,7 +21244,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>258</v>
@@ -21364,7 +21356,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>261</v>
@@ -21476,7 +21468,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>264</v>
@@ -21590,7 +21582,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>268</v>
@@ -21704,7 +21696,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>272</v>
@@ -21818,13 +21810,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>181</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>20</v>
@@ -21932,7 +21924,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>188</v>
@@ -22044,7 +22036,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>189</v>
@@ -22158,7 +22150,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>190</v>
@@ -22274,7 +22266,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>191</v>
@@ -22386,7 +22378,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>194</v>
@@ -22500,7 +22492,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>199</v>
@@ -22526,13 +22518,13 @@
         <v>20</v>
       </c>
       <c r="K183" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M183" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="L183" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="M183" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -22598,13 +22590,13 @@
         <v>20</v>
       </c>
       <c r="AK183" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AL183" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM183" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL183" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AM183" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>20</v>
@@ -22612,7 +22604,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>204</v>
@@ -22724,7 +22716,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>208</v>
@@ -22836,7 +22828,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>209</v>
@@ -22950,7 +22942,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>210</v>
@@ -23066,7 +23058,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>211</v>
@@ -23180,7 +23172,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>217</v>
@@ -23294,7 +23286,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>222</v>
@@ -23406,7 +23398,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>226</v>
@@ -23518,7 +23510,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>227</v>
@@ -23632,7 +23624,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>228</v>
@@ -23748,7 +23740,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>229</v>
@@ -23860,7 +23852,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>235</v>
@@ -23974,7 +23966,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>239</v>
@@ -24086,7 +24078,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>242</v>
@@ -24198,7 +24190,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>245</v>
@@ -24310,7 +24302,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>248</v>
@@ -24422,7 +24414,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>251</v>
@@ -24534,7 +24526,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>255</v>
@@ -24646,7 +24638,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>256</v>
@@ -24760,7 +24752,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>257</v>
@@ -24876,7 +24868,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>258</v>
@@ -24988,7 +24980,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>261</v>
@@ -25100,7 +25092,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>264</v>
@@ -25214,7 +25206,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>268</v>
@@ -25328,7 +25320,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>272</v>
@@ -25442,10 +25434,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -25468,19 +25460,19 @@
         <v>89</v>
       </c>
       <c r="K209" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L209" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L209" t="s" s="2">
+      <c r="N209" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M209" t="s" s="2">
+      <c r="O209" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>20</v>
@@ -25529,7 +25521,7 @@
         <v>20</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>77</v>
@@ -25558,10 +25550,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -25584,16 +25576,16 @@
         <v>89</v>
       </c>
       <c r="K210" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L210" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M210" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L210" t="s" s="2">
+      <c r="N210" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M210" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N210" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
@@ -25643,7 +25635,7 @@
         <v>20</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>77</v>
@@ -25652,7 +25644,7 @@
         <v>88</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AJ210" t="s" s="2">
         <v>20</v>
